--- a/Finance Policies & Procedures/Budgets, Accounting & Awards/DOL428/DOL428 Temp. Budget U.S.-Mexico Trade 2025-12.xlsx
+++ b/Finance Policies & Procedures/Budgets, Accounting & Awards/DOL428/DOL428 Temp. Budget U.S.-Mexico Trade 2025-12.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://partnersnet107.sharepoint.com/sites/FA/Organizational FA/Finance Policies &amp; Procedures/Budgets, Accounting &amp; Awards/DOL428/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="6250" documentId="13_ncr:1_{7D21D2A2-9F1B-47EB-B0AD-400103986469}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{8A5DB6C5-23DF-4A7C-87CE-A902A029FDE8}"/>
+  <xr:revisionPtr revIDLastSave="6262" documentId="13_ncr:1_{7D21D2A2-9F1B-47EB-B0AD-400103986469}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{924F8CAF-068A-40B5-AD7B-5D29DB36442C}"/>
   <bookViews>
-    <workbookView xWindow="11520" yWindow="0" windowWidth="11520" windowHeight="12360" tabRatio="757" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-96" yWindow="-96" windowWidth="23232" windowHeight="12552" tabRatio="757" firstSheet="1" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Budget Summary" sheetId="160" r:id="rId1"/>
@@ -1620,7 +1620,7 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <numFmts count="20">
+  <numFmts count="21">
     <numFmt numFmtId="5" formatCode="&quot;$&quot;#,##0_);\(&quot;$&quot;#,##0\)"/>
     <numFmt numFmtId="7" formatCode="&quot;$&quot;#,##0.00_);\(&quot;$&quot;#,##0.00\)"/>
     <numFmt numFmtId="42" formatCode="_(&quot;$&quot;* #,##0_);_(&quot;$&quot;* \(#,##0\);_(&quot;$&quot;* &quot;-&quot;_);_(@_)"/>
@@ -1641,8 +1641,9 @@
     <numFmt numFmtId="175" formatCode="#,##0.00;[Red]#,##0.00"/>
     <numFmt numFmtId="176" formatCode="#,##0;#,##0;\-"/>
     <numFmt numFmtId="177" formatCode="#,##0.0;#,##0.0;\-"/>
+    <numFmt numFmtId="178" formatCode="#,##0.0000000000"/>
   </numFmts>
-  <fonts count="67" x14ac:knownFonts="1">
+  <fonts count="68" x14ac:knownFonts="1">
     <font>
       <sz val="10"/>
       <name val="Arial"/>
@@ -2086,6 +2087,10 @@
       <sz val="14"/>
       <name val="Arial"/>
       <family val="2"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Arial"/>
     </font>
   </fonts>
   <fills count="36">
@@ -2837,7 +2842,7 @@
       <diagonal/>
     </border>
   </borders>
-  <cellStyleXfs count="331">
+  <cellStyleXfs count="332">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0">
       <alignment vertical="top"/>
     </xf>
@@ -3177,8 +3182,9 @@
     <xf numFmtId="170" fontId="7" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="170" fontId="7" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="173" fontId="7" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="44" fontId="67" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="428">
+  <cellXfs count="432">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="top"/>
     </xf>
@@ -4439,8 +4445,20 @@
     <xf numFmtId="0" fontId="16" fillId="7" borderId="4" xfId="26" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="176" fontId="15" fillId="32" borderId="0" xfId="26" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="178" fontId="15" fillId="32" borderId="0" xfId="26" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="44" fontId="15" fillId="32" borderId="0" xfId="331" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="44" fontId="15" fillId="32" borderId="0" xfId="26" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
   </cellXfs>
-  <cellStyles count="331">
+  <cellStyles count="332">
     <cellStyle name="20% - Accent1 2" xfId="34" xr:uid="{00000000-0005-0000-0000-000000000000}"/>
     <cellStyle name="20% - Accent2 2" xfId="35" xr:uid="{00000000-0005-0000-0000-000001000000}"/>
     <cellStyle name="20% - Accent3 2" xfId="36" xr:uid="{00000000-0005-0000-0000-000002000000}"/>
@@ -4595,6 +4613,7 @@
     <cellStyle name="Comma0 - Style2" xfId="7" xr:uid="{00000000-0005-0000-0000-000098000000}"/>
     <cellStyle name="Curren - Style1" xfId="8" xr:uid="{00000000-0005-0000-0000-000099000000}"/>
     <cellStyle name="Curren - Style3" xfId="9" xr:uid="{00000000-0005-0000-0000-00009A000000}"/>
+    <cellStyle name="Currency" xfId="331" builtinId="4"/>
     <cellStyle name="Currency [0] 2" xfId="175" xr:uid="{00000000-0005-0000-0000-00009B000000}"/>
     <cellStyle name="Currency 10" xfId="176" xr:uid="{00000000-0005-0000-0000-00009C000000}"/>
     <cellStyle name="Currency 100" xfId="177" xr:uid="{00000000-0005-0000-0000-00009D000000}"/>
@@ -5604,7 +5623,7 @@
     <tabColor theme="8" tint="0.59999389629810485"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:U172"/>
+  <dimension ref="A1:AA172"/>
   <sheetFormatPr defaultColWidth="11.44140625" defaultRowHeight="15.3" x14ac:dyDescent="0.4"/>
   <cols>
     <col min="1" max="1" width="21.83203125" style="21" customWidth="1"/>
@@ -5629,7 +5648,12 @@
     <col min="20" max="20" width="20.71875" style="56" customWidth="1"/>
     <col min="21" max="21" width="21.71875" style="78" customWidth="1"/>
     <col min="22" max="22" width="11.44140625" style="33" customWidth="1"/>
-    <col min="23" max="16384" width="11.44140625" style="33"/>
+    <col min="23" max="23" width="11.44140625" style="33"/>
+    <col min="24" max="24" width="19.609375" style="33" bestFit="1" customWidth="1"/>
+    <col min="25" max="25" width="12.71875" style="33" bestFit="1" customWidth="1"/>
+    <col min="26" max="26" width="11.44140625" style="33"/>
+    <col min="27" max="27" width="12.71875" style="33" bestFit="1" customWidth="1"/>
+    <col min="28" max="16384" width="11.44140625" style="33"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:21" ht="17.399999999999999" x14ac:dyDescent="0.4">
@@ -6259,7 +6283,7 @@
         <v>285072.6875</v>
       </c>
     </row>
-    <row r="17" spans="1:21" x14ac:dyDescent="0.4">
+    <row r="17" spans="1:24" x14ac:dyDescent="0.4">
       <c r="A17" s="394" t="s">
         <v>370</v>
       </c>
@@ -6332,7 +6356,7 @@
         <v>200610.05</v>
       </c>
     </row>
-    <row r="18" spans="1:21" x14ac:dyDescent="0.4">
+    <row r="18" spans="1:24" x14ac:dyDescent="0.4">
       <c r="A18" s="395" t="s">
         <v>373</v>
       </c>
@@ -6405,7 +6429,7 @@
         <v>176610.05</v>
       </c>
     </row>
-    <row r="19" spans="1:21" x14ac:dyDescent="0.4">
+    <row r="19" spans="1:24" x14ac:dyDescent="0.4">
       <c r="A19" s="393"/>
       <c r="B19" s="393"/>
       <c r="C19" s="393"/>
@@ -6430,7 +6454,7 @@
       <c r="T19" s="184"/>
       <c r="U19" s="186"/>
     </row>
-    <row r="20" spans="1:21" x14ac:dyDescent="0.4">
+    <row r="20" spans="1:24" x14ac:dyDescent="0.4">
       <c r="A20" s="394" t="s">
         <v>366</v>
       </c>
@@ -6502,7 +6526,7 @@
         <v>221304.515625</v>
       </c>
     </row>
-    <row r="21" spans="1:21" x14ac:dyDescent="0.4">
+    <row r="21" spans="1:24" x14ac:dyDescent="0.4">
       <c r="A21" s="394" t="s">
         <v>367</v>
       </c>
@@ -6574,7 +6598,7 @@
         <v>275401.0176279</v>
       </c>
     </row>
-    <row r="22" spans="1:21" x14ac:dyDescent="0.4">
+    <row r="22" spans="1:24" x14ac:dyDescent="0.4">
       <c r="A22" s="394" t="s">
         <v>368</v>
       </c>
@@ -6646,7 +6670,7 @@
         <v>54096.679046512516</v>
       </c>
     </row>
-    <row r="23" spans="1:21" x14ac:dyDescent="0.4">
+    <row r="23" spans="1:24" x14ac:dyDescent="0.4">
       <c r="A23" s="394" t="s">
         <v>368</v>
       </c>
@@ -6718,7 +6742,7 @@
         <v>132782.70937500001</v>
       </c>
     </row>
-    <row r="24" spans="1:21" ht="15.6" thickBot="1" x14ac:dyDescent="0.45">
+    <row r="24" spans="1:24" ht="15.6" thickBot="1" x14ac:dyDescent="0.45">
       <c r="A24" s="396"/>
       <c r="B24" s="396"/>
       <c r="C24" s="396"/>
@@ -6767,7 +6791,7 @@
         <v>2569156.0904244129</v>
       </c>
     </row>
-    <row r="25" spans="1:21" x14ac:dyDescent="0.4">
+    <row r="25" spans="1:24" x14ac:dyDescent="0.4">
       <c r="A25" s="392"/>
       <c r="B25" s="384"/>
       <c r="C25" s="392"/>
@@ -6792,7 +6816,7 @@
       <c r="T25" s="191"/>
       <c r="U25" s="194"/>
     </row>
-    <row r="26" spans="1:21" x14ac:dyDescent="0.4">
+    <row r="26" spans="1:24" x14ac:dyDescent="0.4">
       <c r="A26" s="394" t="s">
         <v>375</v>
       </c>
@@ -6852,7 +6876,7 @@
         <v>782512.03503124998</v>
       </c>
     </row>
-    <row r="27" spans="1:21" x14ac:dyDescent="0.4">
+    <row r="27" spans="1:24" x14ac:dyDescent="0.4">
       <c r="A27" s="394" t="s">
         <v>374</v>
       </c>
@@ -6912,7 +6936,7 @@
         <v>160437.38111698462</v>
       </c>
     </row>
-    <row r="28" spans="1:21" ht="15.6" thickBot="1" x14ac:dyDescent="0.45">
+    <row r="28" spans="1:24" ht="15.6" thickBot="1" x14ac:dyDescent="0.45">
       <c r="A28" s="397"/>
       <c r="B28" s="396"/>
       <c r="C28" s="397"/>
@@ -6961,7 +6985,7 @@
         <v>942949.41614823462</v>
       </c>
     </row>
-    <row r="29" spans="1:21" x14ac:dyDescent="0.4">
+    <row r="29" spans="1:24" x14ac:dyDescent="0.4">
       <c r="A29" s="392"/>
       <c r="B29" s="384"/>
       <c r="C29" s="392"/>
@@ -6986,7 +7010,7 @@
       <c r="T29" s="208"/>
       <c r="U29" s="211"/>
     </row>
-    <row r="30" spans="1:21" x14ac:dyDescent="0.4">
+    <row r="30" spans="1:24" x14ac:dyDescent="0.4">
       <c r="A30" s="398"/>
       <c r="B30" s="405"/>
       <c r="C30" s="398"/>
@@ -7011,7 +7035,7 @@
       <c r="T30" s="213"/>
       <c r="U30" s="216"/>
     </row>
-    <row r="31" spans="1:21" x14ac:dyDescent="0.4">
+    <row r="31" spans="1:24" x14ac:dyDescent="0.4">
       <c r="A31" s="399" t="s">
         <v>376</v>
       </c>
@@ -7083,7 +7107,7 @@
         <v>1400</v>
       </c>
     </row>
-    <row r="32" spans="1:21" ht="30.6" x14ac:dyDescent="0.4">
+    <row r="32" spans="1:24" ht="30.6" x14ac:dyDescent="0.4">
       <c r="A32" s="399" t="s">
         <v>377</v>
       </c>
@@ -7156,8 +7180,9 @@
         <f>SUM(S32:T32)</f>
         <v>2658</v>
       </c>
-    </row>
-    <row r="33" spans="1:21" x14ac:dyDescent="0.4">
+      <c r="X32" s="429"/>
+    </row>
+    <row r="33" spans="1:27" x14ac:dyDescent="0.4">
       <c r="A33" s="399" t="s">
         <v>378</v>
       </c>
@@ -7230,7 +7255,7 @@
         <v>500</v>
       </c>
     </row>
-    <row r="34" spans="1:21" x14ac:dyDescent="0.4">
+    <row r="34" spans="1:27" x14ac:dyDescent="0.4">
       <c r="A34" s="399" t="s">
         <v>379</v>
       </c>
@@ -7302,7 +7327,7 @@
         <v>370</v>
       </c>
     </row>
-    <row r="35" spans="1:21" x14ac:dyDescent="0.4">
+    <row r="35" spans="1:27" x14ac:dyDescent="0.4">
       <c r="A35" s="398"/>
       <c r="B35" s="405"/>
       <c r="C35" s="398"/>
@@ -7327,7 +7352,7 @@
       <c r="T35" s="218"/>
       <c r="U35" s="221"/>
     </row>
-    <row r="36" spans="1:21" x14ac:dyDescent="0.4">
+    <row r="36" spans="1:27" x14ac:dyDescent="0.4">
       <c r="A36" s="399" t="s">
         <v>380</v>
       </c>
@@ -7399,7 +7424,7 @@
         <v>6182.851584</v>
       </c>
     </row>
-    <row r="37" spans="1:21" ht="30.6" x14ac:dyDescent="0.4">
+    <row r="37" spans="1:27" ht="30.6" x14ac:dyDescent="0.4">
       <c r="A37" s="399" t="s">
         <v>381</v>
       </c>
@@ -7476,7 +7501,7 @@
         <v>11738.585364480001</v>
       </c>
     </row>
-    <row r="38" spans="1:21" x14ac:dyDescent="0.4">
+    <row r="38" spans="1:27" x14ac:dyDescent="0.4">
       <c r="A38" s="399" t="s">
         <v>382</v>
       </c>
@@ -7552,7 +7577,7 @@
         <v>2208.1612800000007</v>
       </c>
     </row>
-    <row r="39" spans="1:21" x14ac:dyDescent="0.4">
+    <row r="39" spans="1:27" x14ac:dyDescent="0.4">
       <c r="A39" s="398"/>
       <c r="B39" s="405"/>
       <c r="C39" s="398"/>
@@ -7577,7 +7602,7 @@
       <c r="T39" s="218"/>
       <c r="U39" s="221"/>
     </row>
-    <row r="40" spans="1:21" x14ac:dyDescent="0.4">
+    <row r="40" spans="1:27" x14ac:dyDescent="0.4">
       <c r="A40" s="399" t="s">
         <v>383</v>
       </c>
@@ -7649,7 +7674,7 @@
         <v>7582.851584</v>
       </c>
     </row>
-    <row r="41" spans="1:21" ht="30.6" x14ac:dyDescent="0.4">
+    <row r="41" spans="1:27" ht="30.6" x14ac:dyDescent="0.4">
       <c r="A41" s="399" t="s">
         <v>384</v>
       </c>
@@ -7727,7 +7752,7 @@
         <v>12528.978790953513</v>
       </c>
     </row>
-    <row r="42" spans="1:21" x14ac:dyDescent="0.4">
+    <row r="42" spans="1:27" x14ac:dyDescent="0.4">
       <c r="A42" s="399" t="s">
         <v>385</v>
       </c>
@@ -7804,7 +7829,7 @@
         <v>2708.1612800000007</v>
       </c>
     </row>
-    <row r="43" spans="1:21" x14ac:dyDescent="0.4">
+    <row r="43" spans="1:27" x14ac:dyDescent="0.4">
       <c r="A43" s="398"/>
       <c r="B43" s="405"/>
       <c r="C43" s="398"/>
@@ -7829,7 +7854,7 @@
       <c r="T43" s="218"/>
       <c r="U43" s="221"/>
     </row>
-    <row r="44" spans="1:21" ht="30.6" x14ac:dyDescent="0.4">
+    <row r="44" spans="1:27" ht="30.6" x14ac:dyDescent="0.4">
       <c r="A44" s="400"/>
       <c r="B44" s="400"/>
       <c r="C44" s="400"/>
@@ -7854,7 +7879,7 @@
       <c r="T44" s="218"/>
       <c r="U44" s="221"/>
     </row>
-    <row r="45" spans="1:21" x14ac:dyDescent="0.4">
+    <row r="45" spans="1:27" x14ac:dyDescent="0.4">
       <c r="A45" s="394" t="s">
         <v>386</v>
       </c>
@@ -7925,7 +7950,7 @@
         <v>6171.1106848864865</v>
       </c>
     </row>
-    <row r="46" spans="1:21" ht="30.6" x14ac:dyDescent="0.4">
+    <row r="46" spans="1:27" ht="30.6" x14ac:dyDescent="0.4">
       <c r="A46" s="394" t="s">
         <v>387</v>
       </c>
@@ -7999,8 +8024,12 @@
         <f>SUM(S46:T46)</f>
         <v>5198.8622575691124</v>
       </c>
-    </row>
-    <row r="47" spans="1:21" x14ac:dyDescent="0.4">
+      <c r="X46" s="428"/>
+      <c r="Y46" s="430"/>
+      <c r="Z46" s="431"/>
+      <c r="AA46" s="431"/>
+    </row>
+    <row r="47" spans="1:27" x14ac:dyDescent="0.4">
       <c r="A47" s="394" t="s">
         <v>388</v>
       </c>
@@ -8074,7 +8103,7 @@
         <v>1698.5855999999999</v>
       </c>
     </row>
-    <row r="48" spans="1:21" ht="30.6" x14ac:dyDescent="0.4">
+    <row r="48" spans="1:27" ht="30.6" x14ac:dyDescent="0.4">
       <c r="A48" s="400"/>
       <c r="B48" s="400"/>
       <c r="C48" s="400"/>
@@ -28350,24 +28379,6 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
-<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
-  <documentManagement>
-    <TaxCatchAll xmlns="dc808d36-874f-4b27-aec2-2fd649817929" xsi:nil="true"/>
-    <SharedWithUsers xmlns="dc808d36-874f-4b27-aec2-2fd649817929">
-      <UserInfo>
-        <DisplayName/>
-        <AccountId xsi:nil="true"/>
-        <AccountType/>
-      </UserInfo>
-    </SharedWithUsers>
-    <lcf76f155ced4ddcb4097134ff3c332f xmlns="f2466082-b6bf-4153-98c3-3c41e85fda18">
-      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    </lcf76f155ced4ddcb4097134ff3c332f>
-  </documentManagement>
-</p:properties>
-</file>
-
-<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
 <ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Document" ma:contentTypeID="0x0101003206C8355D678A459F2EF8957171B231" ma:contentTypeVersion="19" ma:contentTypeDescription="Create a new document." ma:contentTypeScope="" ma:versionID="a5577d833b9f28dcc6be37a04859b9a8">
   <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns2="f2466082-b6bf-4153-98c3-3c41e85fda18" xmlns:ns3="dc808d36-874f-4b27-aec2-2fd649817929" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="ae50cb7862d574a2d96b6910b4abdc85" ns2:_="" ns3:_="">
     <xsd:import namespace="f2466082-b6bf-4153-98c3-3c41e85fda18"/>
@@ -28628,7 +28639,7 @@
 </ct:contentTypeSchema>
 </file>
 
-<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
 <?mso-contentType ?>
 <FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
   <Display>DocumentLibraryForm</Display>
@@ -28637,26 +28648,25 @@
 </FormTemplates>
 </file>
 
-<file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{07684526-136E-4762-8725-48AE18EB803A}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="1ae44f9a-9a67-4ef9-a793-7a625a6828c5"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
-    <ds:schemaRef ds:uri="http://www.w3.org/XML/1998/namespace"/>
-    <ds:schemaRef ds:uri="ceb09a40-ef32-4a87-9fbf-fded1049908e"/>
-    <ds:schemaRef ds:uri="http://purl.org/dc/terms/"/>
-    <ds:schemaRef ds:uri="http://schemas.openxmlformats.org/package/2006/metadata/core-properties"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    <ds:schemaRef ds:uri="http://purl.org/dc/dcmitype/"/>
-    <ds:schemaRef ds:uri="http://purl.org/dc/elements/1.1/"/>
-    <ds:schemaRef ds:uri="dc808d36-874f-4b27-aec2-2fd649817929"/>
-    <ds:schemaRef ds:uri="f2466082-b6bf-4153-98c3-3c41e85fda18"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
+<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
+<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
+  <documentManagement>
+    <TaxCatchAll xmlns="dc808d36-874f-4b27-aec2-2fd649817929" xsi:nil="true"/>
+    <SharedWithUsers xmlns="dc808d36-874f-4b27-aec2-2fd649817929">
+      <UserInfo>
+        <DisplayName/>
+        <AccountId xsi:nil="true"/>
+        <AccountType/>
+      </UserInfo>
+    </SharedWithUsers>
+    <lcf76f155ced4ddcb4097134ff3c332f xmlns="f2466082-b6bf-4153-98c3-3c41e85fda18">
+      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    </lcf76f155ced4ddcb4097134ff3c332f>
+  </documentManagement>
+</p:properties>
 </file>
 
-<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{533F04E4-7B0E-40C3-A2AA-4FD3884C18DC}">
   <ds:schemaRefs>
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/contentType"/>
@@ -28675,10 +28685,29 @@
 </ds:datastoreItem>
 </file>
 
-<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{CE5D101D-F38C-4A99-8C8F-5BE1931D56D1}">
   <ds:schemaRefs>
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
+</file>
+
+<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{07684526-136E-4762-8725-48AE18EB803A}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="1ae44f9a-9a67-4ef9-a793-7a625a6828c5"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
+    <ds:schemaRef ds:uri="http://www.w3.org/XML/1998/namespace"/>
+    <ds:schemaRef ds:uri="ceb09a40-ef32-4a87-9fbf-fded1049908e"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/terms/"/>
+    <ds:schemaRef ds:uri="http://schemas.openxmlformats.org/package/2006/metadata/core-properties"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/dcmitype/"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/elements/1.1/"/>
+    <ds:schemaRef ds:uri="dc808d36-874f-4b27-aec2-2fd649817929"/>
+    <ds:schemaRef ds:uri="f2466082-b6bf-4153-98c3-3c41e85fda18"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
 </file>